--- a/restructuration-sfe/ig/all-profiles.xlsx
+++ b/restructuration-sfe/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2812" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="472">
   <si>
     <t>Property</t>
   </si>
@@ -24,230 +24,245 @@
     <t>ID</t>
   </si>
   <si>
+    <t>EXConceptMetier</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/modele/StructureDefinition/EXConceptMetier</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>0.1.0</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>EX Concept Metier</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2026-07-31T12:42:16+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France (la)</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Exemple concept métier</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>FHIR Version</t>
+  </si>
+  <si>
+    <t>4.0.1</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>logical</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Base Definition</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Base|4.0.1</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Derivation</t>
+  </si>
+  <si>
+    <t>specialization</t>
+  </si>
+  <si>
+    <t>Structure.ID</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Slice Name</t>
+  </si>
+  <si>
+    <t>Alias(s)</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Must Support?</t>
+  </si>
+  <si>
+    <t>Is Modifier?</t>
+  </si>
+  <si>
+    <t>Is Summary?</t>
+  </si>
+  <si>
+    <t>Type(s)</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Requirements</t>
+  </si>
+  <si>
+    <t>Default Value</t>
+  </si>
+  <si>
+    <t>Meaning When Missing</t>
+  </si>
+  <si>
+    <t>Fixed Value</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Minimum Value</t>
+  </si>
+  <si>
+    <t>Maximum Value</t>
+  </si>
+  <si>
+    <t>Maximum Length</t>
+  </si>
+  <si>
+    <t>Binding Strength</t>
+  </si>
+  <si>
+    <t>Binding Description</t>
+  </si>
+  <si>
+    <t>Binding Value Set</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Slicing Discriminator</t>
+  </si>
+  <si>
+    <t>Slicing Description</t>
+  </si>
+  <si>
+    <t>Slicing Ordered</t>
+  </si>
+  <si>
+    <t>Slicing Rules</t>
+  </si>
+  <si>
+    <t>Base Path</t>
+  </si>
+  <si>
+    <t>Base Min</t>
+  </si>
+  <si>
+    <t>Base Max</t>
+  </si>
+  <si>
+    <t>Condition(s)</t>
+  </si>
+  <si>
+    <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
     <t>EXContact</t>
   </si>
   <si>
-    <t>URL</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/modele/StructureDefinition/EXContact</t>
   </si>
   <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>0.1.0</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
     <t>EX Contact</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>draft</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2026-07-31T07:50:12+00:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France (la)</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>Exemple concept métier contact</t>
   </si>
   <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Copyright</t>
-  </si>
-  <si>
-    <t>FHIR Version</t>
-  </si>
-  <si>
-    <t>4.0.1</t>
-  </si>
-  <si>
-    <t>Kind</t>
-  </si>
-  <si>
-    <t>logical</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Base Definition</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/mos/StructureDefinition/Contact|0.1.0-ballot</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Derivation</t>
-  </si>
-  <si>
-    <t>specialization</t>
-  </si>
-  <si>
-    <t>Structure.ID</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Slice Name</t>
-  </si>
-  <si>
-    <t>Alias(s)</t>
-  </si>
-  <si>
-    <t>Label</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Must Support?</t>
-  </si>
-  <si>
-    <t>Is Modifier?</t>
-  </si>
-  <si>
-    <t>Is Summary?</t>
-  </si>
-  <si>
-    <t>Type(s)</t>
-  </si>
-  <si>
-    <t>Short</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Requirements</t>
-  </si>
-  <si>
-    <t>Default Value</t>
-  </si>
-  <si>
-    <t>Meaning When Missing</t>
-  </si>
-  <si>
-    <t>Fixed Value</t>
-  </si>
-  <si>
-    <t>Pattern</t>
-  </si>
-  <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>Minimum Value</t>
-  </si>
-  <si>
-    <t>Maximum Value</t>
-  </si>
-  <si>
-    <t>Maximum Length</t>
-  </si>
-  <si>
-    <t>Binding Strength</t>
-  </si>
-  <si>
-    <t>Binding Description</t>
-  </si>
-  <si>
-    <t>Binding Value Set</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Slicing Discriminator</t>
-  </si>
-  <si>
-    <t>Slicing Description</t>
-  </si>
-  <si>
-    <t>Slicing Ordered</t>
-  </si>
-  <si>
-    <t>Slicing Rules</t>
-  </si>
-  <si>
-    <t>Base Path</t>
-  </si>
-  <si>
-    <t>Base Min</t>
-  </si>
-  <si>
-    <t>Base Max</t>
-  </si>
-  <si>
-    <t>Condition(s)</t>
-  </si>
-  <si>
-    <t>Constraint(s)</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>*</t>
   </si>
   <si>
     <t xml:space="preserve">
 </t>
-  </si>
-  <si>
-    <t>Base</t>
   </si>
   <si>
     <t>EXContact.IdContact</t>
@@ -1607,7 +1622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1789,7 +1804,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24">
@@ -1797,7 +1812,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>156</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25">
@@ -1813,14 +1828,16 @@
         <v>8</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
         <v>9</v>
       </c>
-      <c r="B27" s="2"/>
+      <c r="B27" t="s" s="2">
+        <v>79</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
@@ -1873,7 +1890,7 @@
         <v>22</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>157</v>
+        <v>80</v>
       </c>
     </row>
     <row r="35">
@@ -1901,7 +1918,7 @@
         <v>28</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>158</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
@@ -1909,7 +1926,7 @@
         <v>30</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40">
@@ -1917,7 +1934,7 @@
         <v>31</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>160</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41">
@@ -1933,177 +1950,337 @@
         <v>35</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>161</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>163</v>
+      <c r="A43" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B44" t="s" s="1">
-        <v>1</v>
+      <c r="A44" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>160</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>189</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>190</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>7</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>192</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="B51" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>21</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B58" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>27</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>27</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>194</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>195</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>196</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>34</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B65" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B72" s="2"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B78" s="2"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B79" s="2"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B64" t="s" s="2">
-        <v>161</v>
+      <c r="B85" t="s" s="2">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2113,10 +2290,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK81"/>
+  <dimension ref="A1:AK82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.92578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="14.453125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.83984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="33.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
@@ -2297,7 +2474,7 @@
         <v>73</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M2" t="s" s="2">
         <v>10</v>
@@ -2354,7 +2531,7 @@
         <v>73</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AH2" t="s" s="2">
         <v>74</v>
@@ -2371,13 +2548,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" t="s" s="2">
@@ -2388,25 +2565,25 @@
         <v>74</v>
       </c>
       <c r="H3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="L3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="M3" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="L3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
@@ -2457,13 +2634,13 @@
         <v>73</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="s" s="2">
         <v>73</v>
@@ -2474,7 +2651,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>83</v>
@@ -2491,7 +2668,7 @@
         <v>74</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>73</v>
@@ -2503,13 +2680,13 @@
         <v>73</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
@@ -2560,13 +2737,13 @@
         <v>73</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>73</v>
@@ -2577,13 +2754,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" t="s" s="2">
@@ -2594,7 +2771,7 @@
         <v>74</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>73</v>
@@ -2606,13 +2783,13 @@
         <v>73</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
@@ -2663,13 +2840,13 @@
         <v>73</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>73</v>
@@ -2680,13 +2857,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" t="s" s="2">
@@ -2697,7 +2874,7 @@
         <v>74</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>73</v>
@@ -2709,13 +2886,13 @@
         <v>73</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
@@ -2742,35 +2919,37 @@
         <v>73</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="Z6" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF6" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG6" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="AB6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="AH6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>73</v>
@@ -2781,13 +2960,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" t="s" s="2">
@@ -2798,7 +2977,7 @@
         <v>74</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>73</v>
@@ -2810,7 +2989,7 @@
         <v>73</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
         <v>97</v>
@@ -2843,11 +3022,11 @@
         <v>73</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="Z7" s="2"/>
       <c r="AA7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AB7" t="s" s="2">
         <v>73</v>
@@ -2865,13 +3044,13 @@
         <v>73</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>73</v>
@@ -2882,13 +3061,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" t="s" s="2">
@@ -2899,7 +3078,7 @@
         <v>74</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>73</v>
@@ -2911,13 +3090,13 @@
         <v>73</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -2944,13 +3123,11 @@
         <v>73</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="Z8" s="2"/>
       <c r="AA8" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="AB8" t="s" s="2">
         <v>73</v>
@@ -2968,13 +3145,13 @@
         <v>73</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>73</v>
@@ -2985,13 +3162,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" t="s" s="2">
@@ -3002,7 +3179,7 @@
         <v>74</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>73</v>
@@ -3014,13 +3191,13 @@
         <v>73</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -3047,11 +3224,13 @@
         <v>73</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="Z9" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA9" t="s" s="2">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="AB9" t="s" s="2">
         <v>73</v>
@@ -3069,13 +3248,13 @@
         <v>73</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>73</v>
@@ -3086,13 +3265,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" t="s" s="2">
@@ -3103,7 +3282,7 @@
         <v>74</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>73</v>
@@ -3115,7 +3294,7 @@
         <v>73</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="M10" t="s" s="2">
         <v>109</v>
@@ -3148,13 +3327,11 @@
         <v>73</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z10" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="Z10" s="2"/>
       <c r="AA10" t="s" s="2">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="s" s="2">
         <v>73</v>
@@ -3172,13 +3349,13 @@
         <v>73</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AH10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>73</v>
@@ -3189,13 +3366,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" t="s" s="2">
@@ -3206,10 +3383,10 @@
         <v>74</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>73</v>
@@ -3218,13 +3395,13 @@
         <v>73</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -3251,11 +3428,13 @@
         <v>73</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="Z11" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA11" t="s" s="2">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="AB11" t="s" s="2">
         <v>73</v>
@@ -3279,7 +3458,7 @@
         <v>74</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>73</v>
@@ -3290,7 +3469,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>116</v>
@@ -3307,10 +3486,10 @@
         <v>74</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>73</v>
@@ -3319,13 +3498,13 @@
         <v>73</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -3352,11 +3531,11 @@
         <v>73</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="Z12" s="2"/>
       <c r="AA12" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AB12" t="s" s="2">
         <v>73</v>
@@ -3374,13 +3553,13 @@
         <v>73</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>73</v>
@@ -3391,13 +3570,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" t="s" s="2">
@@ -3408,7 +3587,7 @@
         <v>74</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>73</v>
@@ -3420,7 +3599,7 @@
         <v>73</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>122</v>
@@ -3453,13 +3632,11 @@
         <v>73</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="Z13" s="2"/>
       <c r="AA13" t="s" s="2">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="AB13" t="s" s="2">
         <v>73</v>
@@ -3477,13 +3654,13 @@
         <v>73</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>73</v>
@@ -3494,13 +3671,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
@@ -3511,7 +3688,7 @@
         <v>74</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>73</v>
@@ -3523,13 +3700,13 @@
         <v>73</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -3580,13 +3757,13 @@
         <v>73</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>73</v>
@@ -3597,13 +3774,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -3614,7 +3791,7 @@
         <v>74</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>73</v>
@@ -3626,13 +3803,13 @@
         <v>73</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -3659,11 +3836,13 @@
         <v>73</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="Z15" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA15" t="s" s="2">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="AB15" t="s" s="2">
         <v>73</v>
@@ -3681,13 +3860,13 @@
         <v>73</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>73</v>
@@ -3698,13 +3877,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
@@ -3715,7 +3894,7 @@
         <v>74</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>73</v>
@@ -3727,7 +3906,7 @@
         <v>73</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="M16" t="s" s="2">
         <v>133</v>
@@ -3760,13 +3939,11 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="Z16" s="2"/>
       <c r="AA16" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AB16" t="s" s="2">
         <v>73</v>
@@ -3784,13 +3961,13 @@
         <v>73</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>73</v>
@@ -3801,13 +3978,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -3818,7 +3995,7 @@
         <v>74</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>73</v>
@@ -3830,13 +4007,13 @@
         <v>73</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -3887,13 +4064,13 @@
         <v>73</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>73</v>
@@ -3904,13 +4081,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
@@ -3933,13 +4110,13 @@
         <v>73</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -3990,7 +4167,7 @@
         <v>73</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>74</v>
@@ -4007,13 +4184,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
@@ -4036,13 +4213,13 @@
         <v>73</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -4093,7 +4270,7 @@
         <v>73</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>74</v>
@@ -4110,13 +4287,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -4139,13 +4316,13 @@
         <v>73</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -4196,7 +4373,7 @@
         <v>73</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>74</v>
@@ -4213,13 +4390,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
@@ -4242,13 +4419,13 @@
         <v>73</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -4299,7 +4476,7 @@
         <v>73</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>74</v>
@@ -4316,13 +4493,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -4345,13 +4522,13 @@
         <v>73</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>76</v>
+        <v>157</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -4411,21 +4588,21 @@
         <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -4436,7 +4613,7 @@
         <v>74</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>73</v>
@@ -4448,13 +4625,13 @@
         <v>73</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -4505,30 +4682,30 @@
         <v>73</v>
       </c>
       <c r="AG23" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AH23" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="AK23" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -4539,7 +4716,7 @@
         <v>74</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>73</v>
@@ -4551,13 +4728,13 @@
         <v>73</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -4596,42 +4773,42 @@
         <v>73</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG24" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AE24" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>176</v>
-      </c>
       <c r="AH24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
@@ -4639,10 +4816,10 @@
       </c>
       <c r="F25" s="2"/>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>73</v>
@@ -4654,24 +4831,22 @@
         <v>73</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" s="2"/>
       <c r="Q25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="R25" s="2"/>
       <c r="S25" t="s" s="2">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>73</v>
@@ -4701,36 +4876,36 @@
         <v>73</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="AE25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>73</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>182</v>
@@ -4744,10 +4919,10 @@
       </c>
       <c r="F26" s="2"/>
       <c r="G26" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>73</v>
@@ -4767,14 +4942,16 @@
       <c r="N26" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="O26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="P26" s="2"/>
       <c r="Q26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="R26" s="2"/>
       <c r="S26" t="s" s="2">
-        <v>73</v>
+        <v>161</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>73</v>
@@ -4792,11 +4969,13 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Z26" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA26" t="s" s="2">
-        <v>187</v>
+        <v>73</v>
       </c>
       <c r="AB26" t="s" s="2">
         <v>73</v>
@@ -4817,38 +4996,38 @@
         <v>182</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>188</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>73</v>
@@ -4860,13 +5039,13 @@
         <v>73</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" s="2"/>
@@ -4893,13 +5072,11 @@
         <v>73</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="Z27" s="2"/>
       <c r="AA27" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="AB27" t="s" s="2">
         <v>73</v>
@@ -4917,41 +5094,41 @@
         <v>73</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
-        <v>73</v>
+        <v>202</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>73</v>
@@ -4960,10 +5137,10 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="M28" t="s" s="2">
         <v>203</v>
@@ -4971,9 +5148,7 @@
       <c r="N28" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="O28" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" s="2"/>
       <c r="Q28" t="s" s="2">
         <v>73</v>
@@ -5022,30 +5197,30 @@
         <v>73</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>73</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -5056,7 +5231,7 @@
         <v>74</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>73</v>
@@ -5065,18 +5240,20 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="O29" s="2"/>
       <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
         <v>73</v>
@@ -5131,18 +5308,18 @@
         <v>74</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>188</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>212</v>
@@ -5159,29 +5336,27 @@
         <v>74</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O30" t="s" s="2">
         <v>215</v>
       </c>
+      <c r="O30" s="2"/>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
         <v>73</v>
@@ -5236,18 +5411,18 @@
         <v>74</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>217</v>
@@ -5264,28 +5439,28 @@
         <v>74</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" t="s" s="2">
@@ -5311,13 +5486,13 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>223</v>
+        <v>73</v>
       </c>
       <c r="AB31" t="s" s="2">
         <v>73</v>
@@ -5335,41 +5510,41 @@
         <v>73</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
-        <v>226</v>
+        <v>73</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>73</v>
@@ -5381,16 +5556,16 @@
         <v>73</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
@@ -5416,13 +5591,13 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>73</v>
+        <v>227</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="AB32" t="s" s="2">
         <v>73</v>
@@ -5440,41 +5615,41 @@
         <v>73</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>73</v>
@@ -5486,16 +5661,16 @@
         <v>73</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" t="s" s="2">
@@ -5545,34 +5720,34 @@
         <v>73</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>73</v>
+        <v>193</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
-        <v>73</v>
+        <v>238</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" t="s" s="2">
@@ -5591,15 +5766,17 @@
         <v>73</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>239</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>159</v>
+        <v>240</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
         <v>73</v>
@@ -5636,17 +5813,19 @@
         <v>73</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AD34" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AE34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>74</v>
@@ -5658,22 +5837,20 @@
         <v>73</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="D35" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
         <v>73</v>
       </c>
@@ -5682,10 +5859,10 @@
         <v>74</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>73</v>
@@ -5694,13 +5871,13 @@
         <v>73</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>243</v>
+        <v>176</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>244</v>
+        <v>164</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -5739,19 +5916,17 @@
         <v>73</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="AD35" s="2"/>
       <c r="AE35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>74</v>
@@ -5760,57 +5935,55 @@
         <v>75</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="D36" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="E36" t="s" s="2">
-        <v>246</v>
+        <v>73</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>171</v>
+        <v>248</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="P36" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
       <c r="Q36" t="s" s="2">
         <v>73</v>
       </c>
@@ -5858,7 +6031,7 @@
         <v>73</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>74</v>
@@ -5867,29 +6040,29 @@
         <v>75</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>73</v>
+        <v>251</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>75</v>
@@ -5898,21 +6071,23 @@
         <v>73</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>80</v>
+        <v>176</v>
       </c>
       <c r="M37" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>255</v>
       </c>
@@ -5951,19 +6126,19 @@
         <v>73</v>
       </c>
       <c r="AC37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG37" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>74</v>
@@ -5975,53 +6150,51 @@
         <v>73</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="D38" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Q38" t="s" s="2">
         <v>73</v>
@@ -6058,19 +6231,19 @@
         <v>73</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>73</v>
+        <v>261</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>73</v>
+        <v>262</v>
       </c>
       <c r="AE38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>74</v>
@@ -6082,50 +6255,54 @@
         <v>73</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="D39" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="E39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>168</v>
+        <v>259</v>
       </c>
       <c r="O39" s="2"/>
-      <c r="P39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="Q39" t="s" s="2">
         <v>73</v>
       </c>
@@ -6173,41 +6350,41 @@
         <v>73</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>169</v>
+        <v>257</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>73</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
-        <v>246</v>
+        <v>73</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>73</v>
@@ -6219,17 +6396,15 @@
         <v>73</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" s="2"/>
       <c r="Q40" t="s" s="2">
         <v>73</v>
@@ -6266,78 +6441,76 @@
         <v>73</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="AD40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG40" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="AE40" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>176</v>
-      </c>
       <c r="AH40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
-        <v>73</v>
+        <v>251</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>218</v>
+        <v>176</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="P41" s="2"/>
       <c r="Q41" t="s" s="2">
         <v>73</v>
       </c>
@@ -6361,54 +6534,54 @@
         <v>73</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>272</v>
+        <v>73</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>273</v>
+        <v>73</v>
       </c>
       <c r="AB41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="AE41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>274</v>
+        <v>181</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6419,31 +6592,31 @@
         <v>74</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="P42" t="s" s="2">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="Q42" t="s" s="2">
         <v>73</v>
@@ -6468,13 +6641,13 @@
         <v>73</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>281</v>
+        <v>191</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AB42" t="s" s="2">
         <v>73</v>
@@ -6492,30 +6665,30 @@
         <v>73</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6523,10 +6696,10 @@
       </c>
       <c r="F43" s="2"/>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>73</v>
@@ -6535,22 +6708,22 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="P43" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="Q43" t="s" s="2">
         <v>73</v>
@@ -6560,10 +6733,10 @@
         <v>73</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>291</v>
+        <v>73</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>292</v>
+        <v>73</v>
       </c>
       <c r="V43" t="s" s="2">
         <v>73</v>
@@ -6575,13 +6748,13 @@
         <v>73</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>73</v>
+        <v>286</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>73</v>
+        <v>287</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>73</v>
+        <v>288</v>
       </c>
       <c r="AB43" t="s" s="2">
         <v>73</v>
@@ -6599,30 +6772,30 @@
         <v>73</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6630,10 +6803,10 @@
       </c>
       <c r="F44" s="2"/>
       <c r="G44" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>73</v>
@@ -6642,21 +6815,23 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="P44" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="Q44" t="s" s="2">
         <v>73</v>
       </c>
@@ -6665,10 +6840,10 @@
         <v>73</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>73</v>
+        <v>296</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="V44" t="s" s="2">
         <v>73</v>
@@ -6704,30 +6879,30 @@
         <v>73</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -6738,7 +6913,7 @@
         <v>74</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>73</v>
@@ -6747,18 +6922,20 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O45" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O45" s="2"/>
       <c r="P45" s="2"/>
       <c r="Q45" t="s" s="2">
         <v>73</v>
@@ -6771,7 +6948,7 @@
         <v>73</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>73</v>
+        <v>304</v>
       </c>
       <c r="V45" t="s" s="2">
         <v>73</v>
@@ -6807,30 +6984,30 @@
         <v>73</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B46" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -6841,7 +7018,7 @@
         <v>74</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>73</v>
@@ -6850,20 +7027,18 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N46" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>312</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" s="2"/>
       <c r="Q46" t="s" s="2">
         <v>73</v>
@@ -6912,30 +7087,30 @@
         <v>73</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -6946,105 +7121,101 @@
         <v>74</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="O47" t="s" s="2">
+      <c r="P47" s="2"/>
+      <c r="Q47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R47" s="2"/>
+      <c r="S47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG47" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="P47" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="Q47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="R47" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>314</v>
-      </c>
       <c r="AH47" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7055,36 +7226,38 @@
         <v>74</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="P48" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="O48" t="s" s="2">
+      <c r="Q48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R48" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="P48" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="Q48" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="R48" s="2"/>
       <c r="S48" t="s" s="2">
         <v>73</v>
       </c>
@@ -7128,30 +7301,30 @@
         <v>73</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7171,22 +7344,22 @@
         <v>73</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="O49" t="s" s="2">
+      <c r="P49" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="P49" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="Q49" t="s" s="2">
         <v>73</v>
@@ -7235,7 +7408,7 @@
         <v>73</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>74</v>
@@ -7247,18 +7420,18 @@
         <v>73</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7269,7 +7442,7 @@
         <v>74</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>73</v>
@@ -7278,10 +7451,10 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>218</v>
+        <v>333</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>334</v>
@@ -7318,11 +7491,13 @@
         <v>73</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Z50" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AA50" t="s" s="2">
-        <v>338</v>
+        <v>73</v>
       </c>
       <c r="AB50" t="s" s="2">
         <v>73</v>
@@ -7340,30 +7515,30 @@
         <v>73</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7374,7 +7549,7 @@
         <v>74</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>73</v>
@@ -7383,22 +7558,22 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="P51" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="P51" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="Q51" t="s" s="2">
         <v>73</v>
@@ -7423,13 +7598,11 @@
         <v>73</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="Z51" s="2"/>
       <c r="AA51" t="s" s="2">
-        <v>73</v>
+        <v>343</v>
       </c>
       <c r="AB51" t="s" s="2">
         <v>73</v>
@@ -7447,30 +7620,30 @@
         <v>73</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7481,31 +7654,31 @@
         <v>74</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="O52" t="s" s="2">
+      <c r="P52" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="Q52" t="s" s="2">
         <v>73</v>
@@ -7554,30 +7727,30 @@
         <v>73</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -7588,31 +7761,31 @@
         <v>74</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="O53" t="s" s="2">
+      <c r="P53" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="Q53" t="s" s="2">
         <v>73</v>
@@ -7661,30 +7834,30 @@
         <v>73</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7695,7 +7868,7 @@
         <v>74</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>73</v>
@@ -7704,10 +7877,10 @@
         <v>73</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>183</v>
+        <v>357</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>358</v>
@@ -7715,9 +7888,11 @@
       <c r="N54" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P54" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q54" t="s" s="2">
         <v>73</v>
@@ -7742,13 +7917,13 @@
         <v>73</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>281</v>
+        <v>73</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>361</v>
+        <v>73</v>
       </c>
       <c r="AA54" t="s" s="2">
-        <v>362</v>
+        <v>73</v>
       </c>
       <c r="AB54" t="s" s="2">
         <v>73</v>
@@ -7766,30 +7941,30 @@
         <v>73</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -7800,7 +7975,7 @@
         <v>74</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>73</v>
@@ -7812,19 +7987,17 @@
         <v>73</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="Q55" t="s" s="2">
         <v>73</v>
@@ -7849,13 +8022,13 @@
         <v>73</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>73</v>
+        <v>286</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>73</v>
+        <v>366</v>
       </c>
       <c r="AA55" t="s" s="2">
-        <v>73</v>
+        <v>367</v>
       </c>
       <c r="AB55" t="s" s="2">
         <v>73</v>
@@ -7873,30 +8046,30 @@
         <v>73</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -7907,7 +8080,7 @@
         <v>74</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>73</v>
@@ -7919,19 +8092,19 @@
         <v>73</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="O56" t="s" s="2">
+      <c r="P56" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="Q56" t="s" s="2">
         <v>73</v>
@@ -7980,30 +8153,30 @@
         <v>73</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8026,19 +8199,19 @@
         <v>73</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="O57" t="s" s="2">
+      <c r="P57" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="Q57" t="s" s="2">
         <v>73</v>
@@ -8087,7 +8260,7 @@
         <v>73</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>74</v>
@@ -8099,18 +8272,18 @@
         <v>73</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>381</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8121,7 +8294,7 @@
         <v>74</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>73</v>
@@ -8133,16 +8306,20 @@
         <v>73</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>167</v>
+        <v>382</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2"/>
+        <v>383</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="Q58" t="s" s="2">
         <v>73</v>
       </c>
@@ -8190,41 +8367,41 @@
         <v>73</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>169</v>
+        <v>380</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>73</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
-        <v>246</v>
+        <v>73</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>73</v>
@@ -8236,17 +8413,15 @@
         <v>73</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" s="2"/>
       <c r="Q59" t="s" s="2">
         <v>73</v>
@@ -8295,34 +8470,34 @@
         <v>73</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
-        <v>385</v>
+        <v>251</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" t="s" s="2">
@@ -8335,26 +8510,24 @@
         <v>73</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>386</v>
+        <v>269</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>387</v>
+        <v>270</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="P60" s="2"/>
       <c r="Q60" t="s" s="2">
         <v>73</v>
       </c>
@@ -8402,7 +8575,7 @@
         <v>73</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>388</v>
+        <v>181</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>74</v>
@@ -8414,12 +8587,12 @@
         <v>73</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>389</v>
@@ -8429,7 +8602,7 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>73</v>
+        <v>390</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" t="s" s="2">
@@ -8442,23 +8615,25 @@
         <v>73</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P61" t="s" s="2">
-        <v>392</v>
+        <v>255</v>
       </c>
       <c r="Q61" t="s" s="2">
         <v>73</v>
@@ -8483,31 +8658,31 @@
         <v>73</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>281</v>
+        <v>73</v>
       </c>
       <c r="Z61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG61" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>74</v>
@@ -8519,18 +8694,18 @@
         <v>73</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -8541,7 +8716,7 @@
         <v>74</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>73</v>
@@ -8553,17 +8728,17 @@
         <v>73</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>322</v>
+        <v>188</v>
       </c>
       <c r="M62" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N62" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Q62" t="s" s="2">
         <v>73</v>
@@ -8588,13 +8763,13 @@
         <v>73</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>73</v>
+        <v>286</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>73</v>
+        <v>398</v>
       </c>
       <c r="AA62" t="s" s="2">
-        <v>73</v>
+        <v>399</v>
       </c>
       <c r="AB62" t="s" s="2">
         <v>73</v>
@@ -8612,30 +8787,30 @@
         <v>73</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -8646,7 +8821,7 @@
         <v>74</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>73</v>
@@ -8658,19 +8833,17 @@
         <v>73</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O63" t="s" s="2">
         <v>402</v>
       </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
-        <v>332</v>
+        <v>403</v>
       </c>
       <c r="Q63" t="s" s="2">
         <v>73</v>
@@ -8719,30 +8892,30 @@
         <v>73</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -8753,7 +8926,7 @@
         <v>74</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>73</v>
@@ -8765,17 +8938,19 @@
         <v>73</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P64" t="s" s="2">
-        <v>406</v>
+        <v>337</v>
       </c>
       <c r="Q64" t="s" s="2">
         <v>73</v>
@@ -8824,30 +8999,30 @@
         <v>73</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -8858,7 +9033,7 @@
         <v>74</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>73</v>
@@ -8870,17 +9045,17 @@
         <v>73</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>218</v>
+        <v>357</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q65" t="s" s="2">
         <v>73</v>
@@ -8905,13 +9080,13 @@
         <v>73</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>411</v>
+        <v>73</v>
       </c>
       <c r="AA65" t="s" s="2">
-        <v>412</v>
+        <v>73</v>
       </c>
       <c r="AB65" t="s" s="2">
         <v>73</v>
@@ -8929,30 +9104,30 @@
         <v>73</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -8963,7 +9138,7 @@
         <v>74</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>73</v>
@@ -8975,17 +9150,17 @@
         <v>73</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>309</v>
+        <v>223</v>
       </c>
       <c r="M66" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q66" t="s" s="2">
         <v>73</v>
@@ -9010,13 +9185,13 @@
         <v>73</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>73</v>
+        <v>416</v>
       </c>
       <c r="AA66" t="s" s="2">
-        <v>73</v>
+        <v>417</v>
       </c>
       <c r="AB66" t="s" s="2">
         <v>73</v>
@@ -9034,24 +9209,24 @@
         <v>73</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>417</v>
+        <v>73</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>418</v>
@@ -9068,7 +9243,7 @@
         <v>74</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>73</v>
@@ -9080,7 +9255,7 @@
         <v>73</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>419</v>
@@ -9089,7 +9264,9 @@
         <v>420</v>
       </c>
       <c r="O67" s="2"/>
-      <c r="P67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="Q67" t="s" s="2">
         <v>73</v>
       </c>
@@ -9143,24 +9320,24 @@
         <v>74</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>73</v>
+        <v>422</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9171,7 +9348,7 @@
         <v>74</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>73</v>
@@ -9183,20 +9360,16 @@
         <v>73</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>376</v>
+        <v>308</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="P68" t="s" s="2">
         <v>425</v>
       </c>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
       <c r="Q68" t="s" s="2">
         <v>73</v>
       </c>
@@ -9244,24 +9417,24 @@
         <v>73</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>426</v>
@@ -9278,7 +9451,7 @@
         <v>74</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>73</v>
@@ -9290,16 +9463,20 @@
         <v>73</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>167</v>
+        <v>427</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O69" s="2"/>
-      <c r="P69" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="Q69" t="s" s="2">
         <v>73</v>
       </c>
@@ -9347,41 +9524,41 @@
         <v>73</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>169</v>
+        <v>426</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>73</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
-        <v>246</v>
+        <v>73</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>73</v>
@@ -9393,17 +9570,15 @@
         <v>73</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" s="2"/>
       <c r="Q70" t="s" s="2">
         <v>73</v>
@@ -9452,34 +9627,34 @@
         <v>73</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
-        <v>385</v>
+        <v>251</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" t="s" s="2">
@@ -9492,26 +9667,24 @@
         <v>73</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>386</v>
+        <v>269</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>387</v>
+        <v>270</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="P71" s="2"/>
       <c r="Q71" t="s" s="2">
         <v>73</v>
       </c>
@@ -9559,7 +9732,7 @@
         <v>73</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>388</v>
+        <v>181</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>74</v>
@@ -9571,53 +9744,53 @@
         <v>73</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
-        <v>73</v>
+        <v>390</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>430</v>
+        <v>391</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>431</v>
+        <v>392</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>432</v>
+        <v>254</v>
       </c>
       <c r="P72" t="s" s="2">
-        <v>433</v>
+        <v>255</v>
       </c>
       <c r="Q72" t="s" s="2">
         <v>73</v>
@@ -9642,13 +9815,13 @@
         <v>73</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="AA72" t="s" s="2">
-        <v>223</v>
+        <v>73</v>
       </c>
       <c r="AB72" t="s" s="2">
         <v>73</v>
@@ -9666,24 +9839,24 @@
         <v>73</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>429</v>
+        <v>393</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>434</v>
@@ -9697,10 +9870,10 @@
       </c>
       <c r="F73" s="2"/>
       <c r="G73" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>73</v>
@@ -9712,7 +9885,7 @@
         <v>73</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>315</v>
+        <v>188</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>435</v>
@@ -9749,13 +9922,13 @@
         <v>73</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>73</v>
+        <v>227</v>
       </c>
       <c r="AA73" t="s" s="2">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="AB73" t="s" s="2">
         <v>73</v>
@@ -9776,21 +9949,21 @@
         <v>434</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>439</v>
@@ -9800,14 +9973,14 @@
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
-        <v>440</v>
+        <v>73</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>73</v>
@@ -9819,18 +9992,20 @@
         <v>73</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="P74" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="O74" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="P74" s="2"/>
       <c r="Q74" t="s" s="2">
         <v>73</v>
       </c>
@@ -9884,35 +10059,35 @@
         <v>74</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
-        <v>73</v>
+        <v>445</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>73</v>
@@ -9921,23 +10096,21 @@
         <v>73</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>309</v>
+        <v>446</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="P75" t="s" s="2">
         <v>449</v>
       </c>
+      <c r="P75" s="2"/>
       <c r="Q75" t="s" s="2">
         <v>73</v>
       </c>
@@ -9985,24 +10158,24 @@
         <v>73</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>450</v>
@@ -10019,19 +10192,19 @@
         <v>74</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>451</v>
@@ -10098,18 +10271,18 @@
         <v>74</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>455</v>
@@ -10126,28 +10299,32 @@
         <v>74</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>84</v>
+        <v>381</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>167</v>
+        <v>456</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="Q77" t="s" s="2">
         <v>73</v>
       </c>
@@ -10195,41 +10372,41 @@
         <v>73</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>169</v>
+        <v>455</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>73</v>
+        <v>193</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
-        <v>246</v>
+        <v>73</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>73</v>
@@ -10241,17 +10418,15 @@
         <v>73</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>264</v>
+        <v>172</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" s="2"/>
       <c r="Q78" t="s" s="2">
         <v>73</v>
@@ -10300,34 +10475,34 @@
         <v>73</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
-        <v>385</v>
+        <v>251</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" t="s" s="2">
@@ -10340,26 +10515,24 @@
         <v>73</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>386</v>
+        <v>269</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>387</v>
+        <v>270</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="P79" s="2"/>
       <c r="Q79" t="s" s="2">
         <v>73</v>
       </c>
@@ -10407,7 +10580,7 @@
         <v>73</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>388</v>
+        <v>181</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>74</v>
@@ -10419,52 +10592,54 @@
         <v>73</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
-        <v>73</v>
+        <v>390</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>73</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>459</v>
+        <v>176</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>460</v>
+        <v>391</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>461</v>
+        <v>392</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="P80" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="Q80" t="s" s="2">
         <v>73</v>
       </c>
@@ -10512,24 +10687,24 @@
         <v>73</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>458</v>
+        <v>393</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>463</v>
@@ -10543,10 +10718,10 @@
       </c>
       <c r="F81" s="2"/>
       <c r="G81" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>73</v>
@@ -10555,18 +10730,20 @@
         <v>73</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>218</v>
+        <v>464</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="P81" s="2"/>
       <c r="Q81" t="s" s="2">
         <v>73</v>
@@ -10591,13 +10768,13 @@
         <v>73</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>465</v>
+        <v>73</v>
       </c>
       <c r="AA81" t="s" s="2">
-        <v>466</v>
+        <v>73</v>
       </c>
       <c r="AB81" t="s" s="2">
         <v>73</v>
@@ -10618,16 +10795,119 @@
         <v>463</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F82" s="2"/>
+      <c r="G82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" s="2"/>
+      <c r="Q82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="R82" s="2"/>
+      <c r="S82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
